--- a/artfynd/A 31173-2021 artfynd.xlsx
+++ b/artfynd/A 31173-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31173-2021 artfynd.xlsx
+++ b/artfynd/A 31173-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>64417264</v>
+        <v>73777875</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NV Kastfjärden, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802422.36422507</v>
+        <v>802693</v>
       </c>
       <c r="R2" t="n">
-        <v>7176300.155989834</v>
+        <v>7176316</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +754,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -797,12 +775,7 @@
         <v>64417356</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802730.8280433405</v>
+        <v>802731</v>
       </c>
       <c r="R3" t="n">
-        <v>7176254.927421299</v>
+        <v>7176255</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +846,9 @@
           <t>2013-08-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,12 +879,7 @@
         <v>64417314</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802667.2127351197</v>
+        <v>802667</v>
       </c>
       <c r="R4" t="n">
-        <v>7176392.984424975</v>
+        <v>7176393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +950,9 @@
           <t>2012-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>64417304</v>
+        <v>64417674</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,21 +991,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802502.7357514304</v>
+        <v>802360</v>
       </c>
       <c r="R5" t="n">
-        <v>7176267.118691394</v>
+        <v>7176023</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2012-08-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2012-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-08-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,22 +1077,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>64417331</v>
+        <v>73777877</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1167,40 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NV Kastfjärden, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802733.6971531832</v>
+        <v>802704</v>
       </c>
       <c r="R6" t="n">
-        <v>7176355.969029989</v>
+        <v>7176321</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,22 +1149,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2012-08-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2012-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,56 +1163,50 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64417347</v>
+        <v>64417264</v>
       </c>
       <c r="B7" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1316,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802730.8280433405</v>
+        <v>802422</v>
       </c>
       <c r="R7" t="n">
-        <v>7176254.927421299</v>
+        <v>7176300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,19 +1255,9 @@
           <t>2013-08-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-08-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,15 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>73777877</v>
+        <v>73777878</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,21 +1296,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1429,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802703.8636334147</v>
+        <v>802714</v>
       </c>
       <c r="R8" t="n">
-        <v>7176320.982361579</v>
+        <v>7176263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,19 +1353,9 @@
           <t>2018-09-03</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,37 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>73777878</v>
+        <v>73777876</v>
       </c>
       <c r="B9" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>802713.9812469373</v>
+        <v>802704</v>
       </c>
       <c r="R9" t="n">
-        <v>7176263.186085557</v>
+        <v>7176321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,19 +1450,9 @@
           <t>2018-09-03</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,50 +1479,51 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>73777876</v>
+        <v>64417981</v>
       </c>
       <c r="B10" t="n">
-        <v>89732</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2062</v>
+        <v>112</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Kastfjärden 5.1, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>802703.8636334147</v>
+        <v>801873</v>
       </c>
       <c r="R10" t="n">
-        <v>7176320.982361579</v>
+        <v>7176063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,22 +1550,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,33 +1564,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73777875</v>
+        <v>64418075</v>
       </c>
       <c r="B11" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,34 +1594,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kastfjärden, Vb</t>
+          <t>Kastfjärden 5.1, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>802693.1044104757</v>
+        <v>802097</v>
       </c>
       <c r="R11" t="n">
-        <v>7176316.013134292</v>
+        <v>7175823</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,22 +1654,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-08-06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,33 +1668,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>64418047</v>
+        <v>73777873</v>
       </c>
       <c r="B12" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1853,40 +1698,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kastfjärden 5.1, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>801969.8993612393</v>
+        <v>802237</v>
       </c>
       <c r="R12" t="n">
-        <v>7176010.170014634</v>
+        <v>7175875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,22 +1752,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,34 +1766,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>64418034</v>
+        <v>73777874</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,40 +1795,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kastfjärden 5.1, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>801966.7762048487</v>
+        <v>802076</v>
       </c>
       <c r="R13" t="n">
-        <v>7176037.101571297</v>
+        <v>7175733</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2032,22 +1849,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,62 +1863,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>64417981</v>
+        <v>64418093</v>
       </c>
       <c r="B14" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2121,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>801873.2442067189</v>
+        <v>802052</v>
       </c>
       <c r="R14" t="n">
-        <v>7176063.219492683</v>
+        <v>7175669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,28 +1955,17 @@
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2012-08-06</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2194,15 +1984,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>64418075</v>
+        <v>96318580</v>
       </c>
       <c r="B15" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,43 +1995,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kastfjärden 5.1, Vb</t>
+          <t>Kastfjärden, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>802097.2695745419</v>
+        <v>801934</v>
       </c>
       <c r="R15" t="n">
-        <v>7175823.1014633</v>
+        <v>7175751</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,22 +2053,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,480 +2067,21 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Emil Larsson, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>64418093</v>
-      </c>
-      <c r="B16" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Kastfjärden 5.1, Vb</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>802052.4354956049</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7175669.41669684</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2012-08-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>73777873</v>
-      </c>
-      <c r="B17" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Kastfjärden, Vb</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>802237.1253464884</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7175875.136938488</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>73777874</v>
-      </c>
-      <c r="B18" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Kastfjärden, Vb</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>802075.943733918</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7175733.178214416</v>
-      </c>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2018-09-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Julia Pettersson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>96318580</v>
-      </c>
-      <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Kastfjärden, Vb</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>801934.2965263939</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7175751.032347498</v>
-      </c>
-      <c r="S19" t="n">
-        <v>5</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2021-09-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Emil Larsson</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Emil Larsson, Per-Anders Blomqvist</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
